--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3234,6 +3234,122 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128410566</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90903</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tansen SO, Tansen SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>525542</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6727853</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>90903</v>
+        <v>90995</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>90995</v>
+        <v>91007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91007</v>
+        <v>91009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91009</v>
+        <v>91010</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91010</v>
+        <v>91037</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91037</v>
+        <v>91047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91047</v>
+        <v>91051</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -3239,7 +3239,7 @@
         <v>128410566</v>
       </c>
       <c r="B23" t="n">
-        <v>91051</v>
+        <v>91056</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76104915</v>
+        <v>103370923</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tansen SO, Dlr</t>
+          <t>Tansberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525473.0074085507</v>
+        <v>525536</v>
       </c>
       <c r="R2" t="n">
-        <v>6727798.082117018</v>
+        <v>6727840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt utsprida (på en yta av 25x25m) hela vägen ner till stranden.</t>
+          <t>Växer i ett örtrikt rikmarksstråk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,77 +779,73 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Uno Skog, Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76105214</v>
+        <v>103370966</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tansen SO, Dlr</t>
+          <t>Tansberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525534.9686945388</v>
+        <v>525535</v>
       </c>
       <c r="R3" t="n">
-        <v>6727848.00089261</v>
+        <v>6727851</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,81 +896,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Uno Skog, Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88434774</v>
+        <v>111768503</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tansen SO, Dlr</t>
+          <t>Sågviken, Sågviken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525528.0124992225</v>
+        <v>525545</v>
       </c>
       <c r="R4" t="n">
-        <v>6727860.198449217</v>
+        <v>6727838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,22 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-08</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,69 +1021,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88495391</v>
+        <v>128410566</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tansen SO, Dlr</t>
+          <t>Tansen SO, Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525463.8274422706</v>
+        <v>525542</v>
       </c>
       <c r="R5" t="n">
-        <v>6727777.931462909</v>
+        <v>6727853</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1107,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,65 +1149,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88517422</v>
+        <v>117044231</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tansen SO, Dlr</t>
+          <t>Sågviken, Sågviken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525695.9713609436</v>
+        <v>525556</v>
       </c>
       <c r="R6" t="n">
-        <v>6727907.935457875</v>
+        <v>6727858</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,22 +1223,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-12</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,56 +1247,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Malte Lindberg, Bo karlstens, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88549072</v>
+        <v>76104906</v>
       </c>
       <c r="B7" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1329,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525623.0851515192</v>
+        <v>525500</v>
       </c>
       <c r="R7" t="n">
-        <v>6727807.968419562</v>
+        <v>6727846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,22 +1334,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med blad (30 blommade) på en yta av 10x10m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,15 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88582013</v>
+        <v>76104915</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,16 +1400,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1454,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525597.956461377</v>
+        <v>525473</v>
       </c>
       <c r="R8" t="n">
-        <v>6727960.14109363</v>
+        <v>6727798</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1484,22 +1441,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt utsprida (på en yta av 25x25m) hela vägen ner till stranden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,15 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88581983</v>
+        <v>76105214</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1560,11 +1507,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1579,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525596.8843563613</v>
+        <v>525535</v>
       </c>
       <c r="R9" t="n">
-        <v>6727972.869976863</v>
+        <v>6727848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,22 +1552,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,15 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88582069</v>
+        <v>88434764</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,16 +1613,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1704,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525618.0584601875</v>
+        <v>525510</v>
       </c>
       <c r="R10" t="n">
-        <v>6727962.244000076</v>
+        <v>6727867</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1734,27 +1654,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-10-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>16 ex och 2ex 4m O.</t>
+          <t>På en yta av 1 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,15 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88606396</v>
+        <v>88434774</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,10 +1722,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1830,10 +1739,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525692.9994604094</v>
+        <v>525528</v>
       </c>
       <c r="R11" t="n">
-        <v>6727911.833176443</v>
+        <v>6727860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,22 +1769,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,15 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96203755</v>
+        <v>88434820</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525484.7622800267</v>
+        <v>525437</v>
       </c>
       <c r="R12" t="n">
-        <v>6727801.10489962</v>
+        <v>6727778</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,22 +1871,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2x0,5 m</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,60 +1909,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103370923</v>
+        <v>88495391</v>
       </c>
       <c r="B13" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tansberget, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525535.0279438905</v>
+        <v>525464</v>
       </c>
       <c r="R13" t="n">
-        <v>6727839.673301656</v>
+        <v>6727778</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2100,27 +1978,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:24</t>
+          <t>2020-10-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer i ett örtrikt rikmarksstråk.</t>
+          <t>2020-10-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,78 +1992,68 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Uno Skog, Bo karlstens</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103370966</v>
+        <v>88495505</v>
       </c>
       <c r="B14" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tansberget, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525534.9477830254</v>
+        <v>525483</v>
       </c>
       <c r="R14" t="n">
-        <v>6727850.940037759</v>
+        <v>6727816</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2227,22 +2080,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:33</t>
+          <t>2020-10-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:33</t>
+          <t>2020-10-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Utspridd 4x3 m</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,33 +2099,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog, Bo karlstens</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103533765</v>
+        <v>88517422</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2302,25 +2146,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Falun, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525621.5103802738</v>
+        <v>525696</v>
       </c>
       <c r="R15" t="n">
-        <v>6727959.81930581</v>
+        <v>6727908</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2344,22 +2195,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-09-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-10-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,83 +2209,79 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108785855</v>
+        <v>88548783</v>
       </c>
       <c r="B16" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sågviken, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525533.7329834808</v>
+        <v>525432</v>
       </c>
       <c r="R16" t="n">
-        <v>6727883.753347356</v>
+        <v>6727727</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2468,22 +2305,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-10-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10+50 ex. vid en sten 1m ifrån varandra,+30 ex. 2m längre bort</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,73 +2331,72 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo, Majken Ekstrand</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108799246</v>
+        <v>88581983</v>
       </c>
       <c r="B17" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sågviken, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525553.9400801549</v>
+        <v>525597</v>
       </c>
       <c r="R17" t="n">
-        <v>6727871.160326945</v>
+        <v>6727973</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2589,22 +2420,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2625,61 +2446,67 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Sebastian Kirppu, Linnea Ingelsbo</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109747692</v>
+        <v>88582013</v>
       </c>
       <c r="B18" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tansberget, Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525663.9185648896</v>
+        <v>525598</v>
       </c>
       <c r="R18" t="n">
-        <v>6727930.240273202</v>
+        <v>6727960</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2703,22 +2530,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2727,33 +2544,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Stork</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111768476</v>
+        <v>88582069</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2780,7 +2593,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2793,14 +2606,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sågviken (Sågviken), Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525547</v>
+        <v>525618</v>
       </c>
       <c r="R19" t="n">
-        <v>6727882</v>
+        <v>6727962</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2827,22 +2640,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2020-10-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>16 ex och 2ex 4m O.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2858,73 +2666,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111768503</v>
+        <v>88606396</v>
       </c>
       <c r="B20" t="n">
-        <v>88966</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sågviken (Sågviken), Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525545</v>
+        <v>525693</v>
       </c>
       <c r="R20" t="n">
-        <v>6727838</v>
+        <v>6727912</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2951,22 +2751,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2020-10-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:22</t>
+          <t>2020-10-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,74 +2772,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117044231</v>
+        <v>96183196</v>
       </c>
       <c r="B21" t="n">
-        <v>57297</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sågviken (Sågviken), Dlr</t>
+          <t>Falun, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525556</v>
+        <v>525617</v>
       </c>
       <c r="R21" t="n">
-        <v>6727858</v>
+        <v>6727995</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3073,22 +2851,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3103,27 +2881,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Bo karlstens, Sebastian Kirppu</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117044216</v>
+        <v>96203755</v>
       </c>
       <c r="B22" t="n">
-        <v>97800</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3148,29 +2921,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sågviken (Sågviken), Dlr</t>
+          <t>Tansen SO, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525554</v>
+        <v>525485</v>
       </c>
       <c r="R22" t="n">
-        <v>6727888</v>
+        <v>6727801</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3194,22 +2962,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3218,75 +2976,72 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malte Lindberg, Bo karlstens, Sebastian Kirppu</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128410566</v>
+        <v>103533054</v>
       </c>
       <c r="B23" t="n">
-        <v>91058</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tansen SO, Tansen SO, Dlr</t>
+          <t>Falun, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525542</v>
+        <v>525549</v>
       </c>
       <c r="R23" t="n">
-        <v>6727853</v>
+        <v>6727905</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3310,22 +3065,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2022-09-13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3340,15 +3095,799 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103533765</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>525622</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6727960</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-09-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111768476</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sågviken, Sågviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>525547</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6727882</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117044216</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sågviken, Sågviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>525554</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6727888</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Malte Lindberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Malte Lindberg, Bo karlstens, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>108785855</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sågviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>525534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6727884</v>
+      </c>
+      <c r="S27" t="n">
+        <v>12</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo, Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>108799246</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sågviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>525554</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6727871</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Sebastian Kirppu, Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88549072</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tansen SO, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>525623</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6727808</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-10-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>109747692</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tansberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>525664</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6727931</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Johan Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31622-2023 artfynd.xlsx
+++ b/artfynd/A 31622-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103370923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103370966</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111768503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128410566</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117044231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76104906</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76104915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76105214</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88434764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1799,6 +1849,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88434774</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1906,6 +1961,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88434820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88495391</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88495505</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2225,6 +2295,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88517422</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88548783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88581983</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88582013</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88582069</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88606396</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2890,6 +2990,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96183196</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2992,6 +3097,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96203755</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3104,6 +3214,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103533054</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3216,6 +3331,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103533765</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3336,6 +3456,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111768476</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3452,6 +3577,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117044216</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3572,6 +3702,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108785855</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3688,6 +3823,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108799246</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3790,6 +3930,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88549072</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3888,8 +4033,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109747692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>